--- a/output/2026-10-11_01_Serbia_Branicevski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-11_01_Serbia_Branicevski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -474,7 +474,6 @@
           <t>Profil - prodajno mesto Messer Tehnogas-a</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Požarevac, Braničevski</t>
@@ -490,7 +489,6 @@
           <t>012/555-488</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Punto vendita ufficiale Messer Tehnogas (gas industriali/saldatura). Confermato su planplus.rs, Moravska 121, 12000 Požarevac.</t>
@@ -498,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -508,7 +506,6 @@
           <t>Tehnoplam - diler Messer Tehnogas-a</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Petrovac na Mlavi (Selo Leskovac), Braničevski</t>
@@ -524,7 +521,6 @@
           <t>012/333-075</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dealer Messer Tehnogas confermato su planplus.rs, indirizzo Leskovac bb, 12300 Petrovac na Mlavi.</t>
@@ -542,7 +538,6 @@
           <t>IMK Team - prodajno mesto Messer Tehnogas-a</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Radinac (Smederevo), Braničevski/Podunavski</t>
@@ -558,7 +553,6 @@
           <t>026/4155-551</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Punto vendita Messer Tehnogas (gas tecnici/industriali). Confermato via WebFetch su planplus.rs, Carigradska 25B, 11311 Radinac.</t>
